--- a/it_forms/009_incident_response_after_action_review_questionnaire--it_forms.xlsx
+++ b/it_forms/009_incident_response_after_action_review_questionnaire--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -781,8 +781,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -810,12 +810,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'it_incident',_'label':_'it_incident'}</t>
+          <t>it_incident</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'IT incident', 'label': 'IT incident'}</t>
+          <t>IT incident</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'network_issue',_'label':_'network_issue'}</t>
+          <t>network_issue</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Network issue', 'label': 'Network issue'}</t>
+          <t>Network issue</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'security_incident',_'label':_'security_incident'}</t>
+          <t>security_incident</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Security incident', 'label': 'Security incident'}</t>
+          <t>Security incident</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'success',_'label':_'success'}</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Success', 'label': 'Success'}</t>
+          <t>Success</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'partial_success',_'label':_'partial_success'}</t>
+          <t>partial_success</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Partial success', 'label': 'Partial success'}</t>
+          <t>Partial success</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'failure',_'label':_'failure'}</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Failure', 'label': 'Failure'}</t>
+          <t>Failure</t>
         </is>
       </c>
     </row>
